--- a/data/trans_dic/P19C05-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C05-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,11; 24,11</t>
+          <t>13,22; 23,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,05; 21,1</t>
+          <t>10,77; 20,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 8,92</t>
+          <t>2,78; 8,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 13,24</t>
+          <t>6,75; 13,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,99; 21,69</t>
+          <t>10,43; 20,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,37; 20,6</t>
+          <t>11,4; 20,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,09; 12,25</t>
+          <t>4,85; 11,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 10,93</t>
+          <t>5,84; 10,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,26; 21,21</t>
+          <t>13,2; 20,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,23; 19,26</t>
+          <t>12,1; 19,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 9,07</t>
+          <t>4,39; 9,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,03</t>
+          <t>6,84; 10,92</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 18,28</t>
+          <t>10,63; 18,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,4; 15,03</t>
+          <t>8,31; 15,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,07; 17,88</t>
+          <t>10,54; 17,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 10,32</t>
+          <t>5,46; 10,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,53; 17,06</t>
+          <t>10,35; 16,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,33; 19,81</t>
+          <t>12,4; 19,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,38; 19,05</t>
+          <t>11,67; 19,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,71; 15,61</t>
+          <t>10,91; 15,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,46; 16,1</t>
+          <t>11,62; 16,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,44; 16,45</t>
+          <t>11,62; 16,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,74; 17,11</t>
+          <t>11,84; 16,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,15</t>
+          <t>8,7; 12,18</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,22; 17,91</t>
+          <t>9,55; 17,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,74; 21,29</t>
+          <t>12,72; 21,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,05; 15,06</t>
+          <t>7,34; 14,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,6; 14,63</t>
+          <t>8,66; 14,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,55; 28,82</t>
+          <t>19,09; 28,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,29; 28,36</t>
+          <t>18,58; 28,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 13,78</t>
+          <t>6,71; 13,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,77; 17,68</t>
+          <t>11,88; 17,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,68; 22,28</t>
+          <t>15,3; 22,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,0; 23,4</t>
+          <t>16,89; 23,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,06; 13,1</t>
+          <t>8,19; 13,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,21; 15,28</t>
+          <t>11,08; 15,41</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 21,03</t>
+          <t>12,11; 20,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,47; 19,28</t>
+          <t>10,82; 18,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 16,93</t>
+          <t>9,6; 17,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,03; 16,25</t>
+          <t>9,03; 16,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,1; 27,17</t>
+          <t>17,9; 27,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,74; 21,83</t>
+          <t>13,67; 21,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,91; 20,37</t>
+          <t>12,25; 20,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 13,66</t>
+          <t>6,51; 13,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,5; 23,2</t>
+          <t>16,51; 23,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,11; 19,21</t>
+          <t>13,06; 18,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,23; 17,99</t>
+          <t>12,07; 17,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 13,44</t>
+          <t>8,24; 13,59</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 13,29</t>
+          <t>5,03; 13,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,32; 23,79</t>
+          <t>12,13; 24,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,96; 22,16</t>
+          <t>8,89; 22,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 15,94</t>
+          <t>7,94; 15,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,57; 18,73</t>
+          <t>9,03; 19,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,86; 23,35</t>
+          <t>12,28; 23,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,03; 24,88</t>
+          <t>11,81; 23,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,88; 24,86</t>
+          <t>17,85; 24,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 14,31</t>
+          <t>8,11; 15,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,85; 21,6</t>
+          <t>13,97; 21,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,07; 20,92</t>
+          <t>12,03; 21,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,38; 19,31</t>
+          <t>14,13; 19,71</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,73; 25,67</t>
+          <t>14,36; 24,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,75; 15,95</t>
+          <t>8,14; 15,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,6; 11,67</t>
+          <t>4,4; 10,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,77; 16,05</t>
+          <t>9,91; 16,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,22; 21,28</t>
+          <t>11,48; 21,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,99; 26,36</t>
+          <t>15,13; 25,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,61; 10,33</t>
+          <t>3,75; 10,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,33</t>
+          <t>8,76; 14,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,65; 21,65</t>
+          <t>14,04; 21,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,26; 19,77</t>
+          <t>13,41; 19,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,38</t>
+          <t>4,84; 9,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,06; 14,08</t>
+          <t>9,79; 14,12</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,21; 18,9</t>
+          <t>12,24; 19,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,18; 23,42</t>
+          <t>16,48; 23,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 11,33</t>
+          <t>5,86; 11,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,01; 15,73</t>
+          <t>9,9; 15,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,2; 18,63</t>
+          <t>12,21; 18,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,89; 24,61</t>
+          <t>17,67; 24,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 11,78</t>
+          <t>6,63; 11,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 12,85</t>
+          <t>3,92; 12,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,11; 17,58</t>
+          <t>13,17; 17,86</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,24; 23,15</t>
+          <t>18,12; 22,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 10,72</t>
+          <t>6,7; 10,59</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,8; 12,99</t>
+          <t>6,1; 13,1</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,07; 10,83</t>
+          <t>6,0; 11,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,19; 16,04</t>
+          <t>10,2; 15,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,49; 14,96</t>
+          <t>9,43; 14,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,74</t>
+          <t>2,79; 8,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,7; 16,44</t>
+          <t>10,71; 16,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,07; 18,71</t>
+          <t>13,08; 18,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,59; 14,79</t>
+          <t>9,68; 15,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,77; 11,1</t>
+          <t>7,79; 11,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,15; 12,88</t>
+          <t>9,09; 12,93</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12,49; 16,56</t>
+          <t>12,33; 16,4</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,2; 13,86</t>
+          <t>10,09; 13,89</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,33</t>
+          <t>4,62; 9,19</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,29; 14,88</t>
+          <t>12,36; 15,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,63; 16,52</t>
+          <t>13,72; 16,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,43; 11,87</t>
+          <t>9,51; 11,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,3; 10,78</t>
+          <t>7,38; 10,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,76; 17,67</t>
+          <t>14,82; 17,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,78; 19,64</t>
+          <t>16,83; 19,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,45; 12,95</t>
+          <t>10,34; 12,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,75; 12,23</t>
+          <t>9,11; 12,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,04; 16,0</t>
+          <t>13,99; 15,93</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15,69; 17,75</t>
+          <t>15,71; 17,63</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,33; 12,11</t>
+          <t>10,31; 12,07</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,96; 11,33</t>
+          <t>8,98; 11,25</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23187; 46175</t>
+          <t>25318; 45946</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27690; 52860</t>
+          <t>26987; 52426</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6825; 21867</t>
+          <t>6814; 20996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20776; 40431</t>
+          <t>20615; 41271</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22123; 43637</t>
+          <t>20979; 42141</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28336; 51353</t>
+          <t>28405; 51322</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12528; 30173</t>
+          <t>11959; 29337</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16245; 31424</t>
+          <t>16786; 30673</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52056; 83296</t>
+          <t>51835; 82331</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61115; 96265</t>
+          <t>60452; 96555</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22230; 44588</t>
+          <t>21578; 46879</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40530; 65397</t>
+          <t>40552; 64744</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45018; 74885</t>
+          <t>43562; 75284</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34149; 61085</t>
+          <t>33768; 62876</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36582; 64943</t>
+          <t>38289; 64477</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27353; 52299</t>
+          <t>27656; 51814</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46456; 75254</t>
+          <t>45679; 73595</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53966; 86751</t>
+          <t>54294; 86455</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44757; 74941</t>
+          <t>45913; 75035</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53720; 78281</t>
+          <t>54744; 78072</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97550; 136998</t>
+          <t>98842; 141046</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96558; 138823</t>
+          <t>98112; 139717</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88850; 129468</t>
+          <t>89555; 128028</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>88546; 122579</t>
+          <t>87761; 122800</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21798; 42359</t>
+          <t>22593; 42346</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37422; 62518</t>
+          <t>37367; 64163</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23378; 43742</t>
+          <t>21326; 43411</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25889; 44076</t>
+          <t>26096; 44119</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>53576; 83231</t>
+          <t>55144; 82655</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60126; 93249</t>
+          <t>61082; 92690</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21407; 42399</t>
+          <t>20648; 42662</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39478; 59261</t>
+          <t>39827; 59434</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82379; 117057</t>
+          <t>80362; 117667</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>105839; 145624</t>
+          <t>105124; 145955</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48230; 78397</t>
+          <t>49009; 80376</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71321; 97270</t>
+          <t>70490; 98076</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33032; 56252</t>
+          <t>32406; 56069</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32781; 60369</t>
+          <t>33884; 58325</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31690; 55873</t>
+          <t>31697; 57502</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28000; 50391</t>
+          <t>28013; 51095</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54225; 81382</t>
+          <t>53617; 82241</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47110; 74831</t>
+          <t>46855; 75296</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41546; 71065</t>
+          <t>42738; 73243</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28843; 64696</t>
+          <t>30828; 63910</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93546; 131585</t>
+          <t>93595; 130775</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85982; 126017</t>
+          <t>85638; 122558</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83031; 122139</t>
+          <t>81913; 120472</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>60637; 105289</t>
+          <t>64561; 106518</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8688; 22623</t>
+          <t>8557; 23024</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23659; 45690</t>
+          <t>23303; 46551</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10681; 26425</t>
+          <t>10600; 26471</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13646; 26854</t>
+          <t>13370; 25537</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14911; 32570</t>
+          <t>15696; 33399</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25030; 45427</t>
+          <t>23901; 45844</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17507; 36206</t>
+          <t>17184; 34733</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>36165; 50291</t>
+          <t>36102; 50363</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27791; 49254</t>
+          <t>27925; 51695</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53537; 83508</t>
+          <t>54006; 84468</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31961; 55393</t>
+          <t>31856; 57117</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>53291; 71585</t>
+          <t>52390; 73062</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27878; 48583</t>
+          <t>27186; 47159</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19369; 39864</t>
+          <t>20337; 39843</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10738; 27267</t>
+          <t>10284; 25575</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24781; 40736</t>
+          <t>25156; 41267</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22939; 43517</t>
+          <t>23482; 44253</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42341; 69809</t>
+          <t>40064; 67464</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8911; 25519</t>
+          <t>9273; 26048</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21217; 35310</t>
+          <t>21587; 34847</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53747; 85261</t>
+          <t>55285; 84982</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68280; 101756</t>
+          <t>69020; 101481</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22957; 45109</t>
+          <t>23268; 46053</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50296; 70397</t>
+          <t>48941; 70617</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>56705; 87753</t>
+          <t>56844; 88664</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>93047; 134688</t>
+          <t>94749; 136249</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25865; 50106</t>
+          <t>25931; 50841</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>60017; 94345</t>
+          <t>59384; 94391</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>65813; 100463</t>
+          <t>65839; 100344</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>111958; 154076</t>
+          <t>110637; 153097</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31584; 57372</t>
+          <t>32312; 57707</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>32732; 106422</t>
+          <t>32434; 105539</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>131583; 176480</t>
+          <t>132203; 179212</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>219121; 278074</t>
+          <t>217591; 275236</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63543; 99589</t>
+          <t>62265; 98417</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>97093; 185436</t>
+          <t>87121; 187095</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>31919; 56934</t>
+          <t>31511; 58281</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>64588; 101701</t>
+          <t>64664; 100117</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60773; 95793</t>
+          <t>60380; 93776</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21257; 79422</t>
+          <t>25395; 78796</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>63376; 97380</t>
+          <t>63471; 96882</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>91781; 131383</t>
+          <t>91854; 130798</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>66273; 102249</t>
+          <t>66913; 103872</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>54723; 78107</t>
+          <t>54867; 79113</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>102254; 143977</t>
+          <t>101670; 144530</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>166883; 221239</t>
+          <t>164690; 219077</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>135796; 184505</t>
+          <t>134326; 185021</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>72784; 150426</t>
+          <t>74538; 148241</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>301710; 365333</t>
+          <t>303299; 369199</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>397309; 481554</t>
+          <t>400015; 479745</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>251292; 316354</t>
+          <t>253386; 318699</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>244798; 361711</t>
+          <t>247443; 360860</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>404636; 484194</t>
+          <t>406123; 483010</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>528109; 617858</t>
+          <t>529515; 620549</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>299632; 371248</t>
+          <t>296557; 369711</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>312993; 437865</t>
+          <t>326155; 438160</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>729461; 831117</t>
+          <t>726894; 827500</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>950909; 1076018</t>
+          <t>952121; 1068420</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>571410; 669867</t>
+          <t>570141; 667864</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>620979; 785501</t>
+          <t>622322; 779952</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C05-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C05-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,22; 23,99</t>
+          <t>13,25; 23,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,77; 20,92</t>
+          <t>10,79; 21,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 8,56</t>
+          <t>2,79; 9,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 13,51</t>
+          <t>7,71; 14,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,43; 20,94</t>
+          <t>10,97; 20,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,4; 20,59</t>
+          <t>11,19; 21,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,91</t>
+          <t>5,14; 11,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,66</t>
+          <t>5,35; 9,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,2; 20,96</t>
+          <t>13,43; 20,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,1; 19,32</t>
+          <t>12,12; 19,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,54</t>
+          <t>4,63; 9,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,84; 10,92</t>
+          <t>7,1; 10,89</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,63; 18,37</t>
+          <t>10,74; 18,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,31; 15,47</t>
+          <t>8,2; 14,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,54; 17,75</t>
+          <t>10,18; 17,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,22</t>
+          <t>5,86; 10,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,35; 16,68</t>
+          <t>10,7; 16,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,4; 19,75</t>
+          <t>12,67; 20,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,67; 19,08</t>
+          <t>11,49; 18,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,91; 15,57</t>
+          <t>10,88; 15,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,62; 16,57</t>
+          <t>11,67; 16,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,62; 16,55</t>
+          <t>11,55; 16,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,84; 16,92</t>
+          <t>11,76; 17,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,18</t>
+          <t>9,04; 12,59</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,55; 17,9</t>
+          <t>9,16; 18,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,72; 21,85</t>
+          <t>12,59; 21,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 14,94</t>
+          <t>7,95; 15,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,66; 14,65</t>
+          <t>8,77; 14,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 28,62</t>
+          <t>19,04; 28,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,58; 28,19</t>
+          <t>18,99; 29,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 13,86</t>
+          <t>6,87; 13,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,88; 17,73</t>
+          <t>11,94; 17,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,3; 22,4</t>
+          <t>15,71; 22,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,89; 23,45</t>
+          <t>17,13; 24,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,19; 13,43</t>
+          <t>8,17; 12,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 15,41</t>
+          <t>11,09; 15,19</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,11; 20,96</t>
+          <t>12,18; 20,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 18,63</t>
+          <t>10,65; 18,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 17,42</t>
+          <t>9,63; 17,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,03; 16,48</t>
+          <t>8,74; 16,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,9; 27,46</t>
+          <t>17,61; 27,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,67; 21,96</t>
+          <t>13,59; 21,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,25; 20,99</t>
+          <t>12,5; 21,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 13,5</t>
+          <t>10,27; 15,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,51; 23,06</t>
+          <t>16,62; 22,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,06; 18,69</t>
+          <t>13,24; 19,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,07; 17,74</t>
+          <t>12,28; 18,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,24; 13,59</t>
+          <t>10,01; 14,51</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 13,52</t>
+          <t>5,2; 13,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,13; 24,24</t>
+          <t>11,96; 22,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 22,2</t>
+          <t>8,96; 22,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,94; 15,16</t>
+          <t>7,18; 14,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,03; 19,2</t>
+          <t>8,84; 19,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,28; 23,56</t>
+          <t>12,81; 23,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,81; 23,87</t>
+          <t>12,06; 23,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,85; 24,9</t>
+          <t>17,1; 23,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,11; 15,02</t>
+          <t>8,07; 14,69</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,97; 21,85</t>
+          <t>13,9; 21,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,03; 21,58</t>
+          <t>12,41; 20,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,13; 19,71</t>
+          <t>13,55; 18,61</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,36; 24,92</t>
+          <t>14,65; 26,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,14; 15,94</t>
+          <t>7,94; 16,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,4; 10,95</t>
+          <t>4,24; 10,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,91; 16,26</t>
+          <t>9,82; 16,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,48; 21,64</t>
+          <t>10,97; 21,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,13; 25,47</t>
+          <t>16,25; 25,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,75; 10,54</t>
+          <t>3,7; 10,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,76; 14,15</t>
+          <t>8,45; 14,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,04; 21,58</t>
+          <t>14,05; 21,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,41; 19,71</t>
+          <t>13,48; 19,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,84; 9,58</t>
+          <t>4,78; 9,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,79; 14,12</t>
+          <t>10,09; 14,01</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,24; 19,1</t>
+          <t>12,41; 18,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,48; 23,69</t>
+          <t>16,23; 23,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,86; 11,49</t>
+          <t>6,07; 11,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,9; 15,74</t>
+          <t>10,23; 15,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,21; 18,6</t>
+          <t>12,17; 18,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,67; 24,46</t>
+          <t>17,81; 24,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,63; 11,85</t>
+          <t>6,47; 11,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,92; 12,74</t>
+          <t>10,52; 15,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,17; 17,86</t>
+          <t>13,1; 17,4</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,12; 22,92</t>
+          <t>18,08; 23,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,7; 10,59</t>
+          <t>6,9; 10,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,1; 13,1</t>
+          <t>11,02; 14,58</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,0; 11,09</t>
+          <t>5,9; 10,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,2; 15,79</t>
+          <t>10,39; 15,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,43; 14,65</t>
+          <t>9,6; 15,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,79; 8,67</t>
+          <t>6,11; 9,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,71; 16,35</t>
+          <t>10,49; 16,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,08; 18,62</t>
+          <t>12,92; 18,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,68; 15,02</t>
+          <t>9,63; 14,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,79; 11,24</t>
+          <t>7,67; 11,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,09; 12,93</t>
+          <t>9,14; 12,92</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12,33; 16,4</t>
+          <t>12,26; 16,37</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,09; 13,89</t>
+          <t>10,13; 13,88</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,19</t>
+          <t>7,36; 9,84</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,36; 15,04</t>
+          <t>12,22; 15,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,72; 16,46</t>
+          <t>13,75; 16,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,51; 11,96</t>
+          <t>9,57; 11,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,38; 10,76</t>
+          <t>9,37; 11,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,82; 17,62</t>
+          <t>14,73; 17,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,83; 19,72</t>
+          <t>16,74; 19,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,34; 12,89</t>
+          <t>10,39; 12,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,11; 12,24</t>
+          <t>11,31; 13,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,99; 15,93</t>
+          <t>13,91; 15,89</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15,71; 17,63</t>
+          <t>15,67; 17,67</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,31; 12,07</t>
+          <t>10,38; 12,15</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,98; 11,25</t>
+          <t>10,62; 12,01</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29337</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>22875</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52021</t>
+          <t>54252</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25318; 45946</t>
+          <t>25370; 45401</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26987; 52426</t>
+          <t>27034; 54100</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6814; 20996</t>
+          <t>6849; 22189</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20615; 41271</t>
+          <t>23191; 42159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20979; 42141</t>
+          <t>22081; 42183</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28405; 51322</t>
+          <t>27887; 52952</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11959; 29337</t>
+          <t>12649; 29503</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16786; 30673</t>
+          <t>16542; 30163</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51835; 82331</t>
+          <t>52749; 81890</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60452; 96555</t>
+          <t>60590; 98884</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21578; 46879</t>
+          <t>22770; 44816</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40552; 64744</t>
+          <t>43328; 66457</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38287</t>
+          <t>41977</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>65965</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>104252</t>
+          <t>112515</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43562; 75284</t>
+          <t>44017; 75294</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33768; 62876</t>
+          <t>33332; 60623</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38289; 64477</t>
+          <t>36983; 65035</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27656; 51814</t>
+          <t>30368; 55324</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45679; 73595</t>
+          <t>47202; 73984</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54294; 86455</t>
+          <t>55461; 87682</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45913; 75035</t>
+          <t>45185; 74363</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54744; 78072</t>
+          <t>57848; 83617</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>98842; 141046</t>
+          <t>99270; 139759</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>98112; 139717</t>
+          <t>97541; 140503</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89555; 128028</t>
+          <t>88947; 128587</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87761; 122800</t>
+          <t>94908; 132179</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>33897</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49015</t>
+          <t>50369</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83345</t>
+          <t>84266</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22593; 42346</t>
+          <t>21675; 43092</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37367; 64163</t>
+          <t>36967; 62839</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21326; 43411</t>
+          <t>23105; 44534</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26096; 44119</t>
+          <t>26334; 43986</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55144; 82655</t>
+          <t>55001; 83598</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61082; 92690</t>
+          <t>62434; 95390</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20648; 42662</t>
+          <t>21129; 42638</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39827; 59434</t>
+          <t>40793; 61136</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>80362; 117667</t>
+          <t>82530; 117968</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>105124; 145955</t>
+          <t>106627; 149968</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49009; 80376</t>
+          <t>48884; 77485</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>70490; 98076</t>
+          <t>71220; 97492</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37794</t>
+          <t>43399</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>48686</t>
+          <t>52505</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86480</t>
+          <t>95904</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32406; 56069</t>
+          <t>32593; 55465</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33884; 58325</t>
+          <t>33341; 58898</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31697; 57502</t>
+          <t>31767; 58006</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28013; 51095</t>
+          <t>32399; 59601</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53617; 82241</t>
+          <t>52760; 81437</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46855; 75296</t>
+          <t>46583; 74600</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42738; 73243</t>
+          <t>43624; 73795</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30828; 63910</t>
+          <t>43091; 63701</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93595; 130775</t>
+          <t>94248; 130104</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85638; 122558</t>
+          <t>86842; 126460</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>81913; 120472</t>
+          <t>83354; 122445</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>64561; 106518</t>
+          <t>79151; 114666</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>42651</t>
+          <t>44433</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61504</t>
+          <t>64247</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8557; 23024</t>
+          <t>8847; 23506</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23303; 46551</t>
+          <t>22965; 43991</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10600; 26471</t>
+          <t>10681; 26566</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13370; 25537</t>
+          <t>13585; 26762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15696; 33399</t>
+          <t>15365; 33706</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23901; 45844</t>
+          <t>24920; 45583</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17184; 34733</t>
+          <t>17544; 34544</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>36102; 50363</t>
+          <t>37585; 52171</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27925; 51695</t>
+          <t>27788; 50567</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54006; 84468</t>
+          <t>53741; 84017</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31856; 57117</t>
+          <t>32855; 55255</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52390; 73062</t>
+          <t>55438; 76116</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32214</t>
+          <t>32163</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>27757</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>59658</t>
+          <t>59920</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27186; 47159</t>
+          <t>27729; 50550</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20337; 39843</t>
+          <t>19853; 40506</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10284; 25575</t>
+          <t>9900; 25545</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25156; 41267</t>
+          <t>24520; 41652</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23482; 44253</t>
+          <t>22430; 44094</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40064; 67464</t>
+          <t>43029; 67626</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9273; 26048</t>
+          <t>9149; 26314</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21587; 34847</t>
+          <t>21245; 35429</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>55285; 84982</t>
+          <t>55319; 84013</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69020; 101481</t>
+          <t>69406; 100367</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23268; 46053</t>
+          <t>22973; 46036</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>48941; 70617</t>
+          <t>50576; 70219</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75453</t>
+          <t>89747</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>74969</t>
+          <t>93179</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>150422</t>
+          <t>182926</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>56844; 88664</t>
+          <t>57638; 88150</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>94749; 136249</t>
+          <t>93326; 134689</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25931; 50841</t>
+          <t>26854; 50410</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59384; 94391</t>
+          <t>71374; 110135</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>65839; 100344</t>
+          <t>65623; 98779</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>110637; 153097</t>
+          <t>111461; 154041</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32312; 57707</t>
+          <t>31502; 57070</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>32434; 105539</t>
+          <t>77958; 111652</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>132203; 179212</t>
+          <t>131464; 174612</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>217591; 275236</t>
+          <t>217214; 276862</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62265; 98417</t>
+          <t>64155; 99053</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>87121; 187095</t>
+          <t>158565; 209769</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54347</t>
+          <t>59966</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>66517</t>
+          <t>75876</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>120864</t>
+          <t>135841</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>31511; 58281</t>
+          <t>30995; 57610</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>64664; 100117</t>
+          <t>65892; 100307</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60380; 93776</t>
+          <t>61464; 96352</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25395; 78796</t>
+          <t>47094; 74521</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>63471; 96882</t>
+          <t>62138; 95400</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>91854; 130798</t>
+          <t>90701; 130593</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>66913; 103872</t>
+          <t>66604; 100944</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>54867; 79113</t>
+          <t>62112; 90079</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>101670; 144530</t>
+          <t>102225; 144415</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>164690; 219077</t>
+          <t>163788; 218765</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>134326; 185021</t>
+          <t>134880; 184857</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>74538; 148241</t>
+          <t>116454; 155667</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>320615</t>
+          <t>352339</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>397930</t>
+          <t>437533</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>718545</t>
+          <t>789872</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>303299; 369199</t>
+          <t>299928; 369344</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>400015; 479745</t>
+          <t>400853; 482157</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>253386; 318699</t>
+          <t>254844; 317446</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>247443; 360860</t>
+          <t>318270; 390567</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>406123; 483010</t>
+          <t>403825; 477766</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>529515; 620549</t>
+          <t>526808; 614330</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>296557; 369711</t>
+          <t>298011; 372425</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>326155; 438160</t>
+          <t>410127; 473377</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>726894; 827500</t>
+          <t>722756; 825630</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>952121; 1068420</t>
+          <t>949783; 1070834</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>570141; 667864</t>
+          <t>574241; 672027</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>622322; 779952</t>
+          <t>746058; 843528</t>
         </is>
       </c>
     </row>
